--- a/outputs/daily/hr_rankings_2026-07-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-26.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
